--- a/exercices/equipe_B_lignes_bus.xlsx
+++ b/exercices/equipe_B_lignes_bus.xlsx
@@ -8,7 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lignes_bus" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📋 Consignes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="passe_par" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ref_communes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📋 Consignes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,26 +29,66 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <i val="1"/>
       <color rgb="00888888"/>
-      <sz val="8"/>
+      <sz val="9"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="0015803D"/>
+      <color rgb="00f59e0b"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="006b21a8"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00333333"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0015803d"/>
       <sz val="14"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00888888"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00B45309"/>
+      <color rgb="00009fe3"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0095c11f"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00e53e3e"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -55,12 +97,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0015803D"/>
+        <fgColor rgb="0095c11f"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3F4F6"/>
+        <fgColor rgb="004a4a4a"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00f59e0b"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006b21a8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00fef3c7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00f3e8ff"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00f9fafb"/>
       </patternFill>
     </fill>
   </fills>
@@ -74,37 +146,70 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D1D5DB"/>
+        <color rgb="00CCCCCC"/>
       </left>
       <right style="thin">
-        <color rgb="00D1D5DB"/>
+        <color rgb="00CCCCCC"/>
       </right>
       <top style="thin">
-        <color rgb="00D1D5DB"/>
+        <color rgb="00CCCCCC"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D1D5DB"/>
+        <color rgb="00CCCCCC"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -471,224 +576,69 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id_ligne</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>numero_ligne</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>id_prestataire</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>communes_desservies</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>type_service</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>actif</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>PK · Texte</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Texte</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>PK — ex : L389</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>numéro affiché</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>FK → prestataires</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Texte (séparé par /)</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Énumération</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Booléen 0/1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="n"/>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="n"/>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n"/>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n"/>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n"/>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n"/>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n"/>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n"/>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n"/>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n"/>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n"/>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="n"/>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n"/>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="n"/>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n"/>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="n"/>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n"/>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n"/>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="n"/>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="3" t="n"/>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>local / regional</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>0 ou 1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -701,51 +651,601 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>id_ligne</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>id_commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>FK → lignes_bus</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>FK → ref_communes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>L389</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>L389</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>C002</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>L389</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>C003</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>L169</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>C004</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>L169</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>C005</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>L169</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>C006</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>L323</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>C003</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>L323</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>C002</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>L191</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>C003</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>L191</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>C004</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>L289</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>C006</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>L289</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>C005</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>L058</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>C003</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>L058</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>C002</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>L058</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>L160</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>C007</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>L160</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>C008</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>L160</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>C005</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>id_commune</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>nom_commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>nom officiel</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Boulogne-Billancourt</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>C002</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Issy-les-Moulineaux</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>C003</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Meudon</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>C004</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Clamart</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>C005</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Châtillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>C006</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Vanves</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>C007</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Montrouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>C008</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Malakoff</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>ÉQUIPE B — Lignes de Bus</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Votre mission : renseigner la table des lignes de bus desservies par la DIRMOB.</t>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>Équipe B — Lignes de bus</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>DIRMOB — Formation données robustes · Serious Game</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Règles : 1 ligne = 1 ligne de bus · id_ligne unique (ex : L389) · id_prestataire doit exister dans la table de l'Équipe A.</t>
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>VOTRE MISSION</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>type_service valeurs autorisées : local | régional</t>
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Vous gérez les lignes de bus de la DIRMOB. Vous devez concevoir TROIS tables :</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • lignes_bus      : une ligne de bus par enregistrement</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>⚠ Attendez que l'Équipe A vous communique ses IDs prestataires avant de remplir la colonne id_prestataire.</t>
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • passe_par       : table de liaison entre lignes et communes (1 ligne = 1 passage)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>⚠ Une fois vos IDs de lignes définis, communiquez-les à l'Équipe C (Réclamations) — ils en ont besoin.</t>
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • ref_communes    : référentiel des communes (pré-rempli)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>L'Équipe A vous donnera ses IDs de prestataires — attendez-les avant de remplir id_prestataire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Une fois vos IDs de lignes définis, communiquez-les à voix haute à tout le monde.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>FEUILLE lignes_bus</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  id_ligne        Identifiant unique (ex : L389) — c'est votre PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  numero_ligne    Le numéro affiché (389, 169, 58…)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  id_prestataire  FK → prestataires de l'Équipe A — attendre leurs IDs</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  type_service    local ou regional — liste fermée</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  actif           1 si la ligne circule, 0 si suspendue</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>FEUILLE passe_par  (à compléter avec vos id_ligne)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  id_ligne    FK → lignes_bus — l'identifiant de la ligne</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  id_commune  FK → ref_communes — l'identifiant de la commune</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  → Pourquoi cette table ? =COUNTIF(passe_par!B:B,"C003") = toutes les lignes passant par Meudon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Sans elle : impossible de filtrer depuis "Meudon/Issy/Boulogne" dans une cellule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>FEUILLE ref_communes  (pré-remplie — ne pas modifier)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  C001 Boulogne-Billancourt  · C002 Issy-les-Moulineaux  · C003 Meudon  · C004 Clamart</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  C005 Châtillon  · C006 Vanves  · C007 Montrouge  · C008 Malakoff</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>RÈGLES ABSOLUES</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • 1 cellule = 1 valeur — jamais de valeurs séparées par / ou ,</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Pas de couleur pour porter une information</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Pas de lignes vides entre les données</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Les dates au format YYYY-MM-DD</t>
         </is>
       </c>
     </row>
